--- a/data/trending_integrated_20260911_13.xlsx
+++ b/data/trending_integrated_20260911_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F2" t="n">
         <v>92</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207531226205</v>
+        <v>207656301485</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 다음 시장으로 사이버 보안을 지목한 젠슨 황 언급, 공급 계약 및 대규모 매집 사례를 근거로 급등 전망.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 테마 부각. 엑스게이트의 양자보안 관련 독점적 지위 강조. 594억 공급계약 및 모건스텐리 대량 매집 공시 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버보안', '젠슨황', '공급계약']</t>
+          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15570</v>
+        <v>15370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+28.78%</t>
+          <t>+27.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>376</v>
       </c>
       <c r="F3" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G3" t="n">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="H3" t="n">
         <v>3.14</v>
@@ -702,7 +702,7 @@
         <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>188850000000</v>
+        <v>190397000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>국제 유가 급등에 따른 급등세. 사우디, 중동 전쟁 관련 호재 및 외국인 대량 매수 유입.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제 유가', '중동 전쟁', '외국인 매수']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -755,20 +755,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.97%</t>
+          <t>+19.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>94709000000</v>
+        <v>95411681247</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
         <v>-1884000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자컴퓨터 관련 정부 지원 및 모건스탠리 매집 공시를 통한 상승 기대감 형성. 거래량 증가.</t>
+          <t>미국 정부 양자컴퓨터 보조금 지원 및 공급 계약 체결 사실 기반 상승 기대. 모건스텐리 대량 매집 공시 확인. 양자보안 테마 대장주로서의 강점 부각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '공급계약', '모건스탠리']</t>
+          <t>['양자컴퓨터', '공급 계약', '모건스텐리']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137600</v>
+        <v>136300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.93%</t>
+          <t>+17.20%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>116300</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>444926481750</v>
+        <v>450769000000</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>52000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매출 호조 및 애플 관련 호재 가능성 언급. 거래량 부족 및 단기 급등에 대한 경계심 혼재.</t>
+          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['매출 호조', '애플', '거래량']</t>
+          <t>['공급 부족', '3상', '애플']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7640</v>
+        <v>7490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.03%</t>
+          <t>+14.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="H6" t="n">
         <v>2.15</v>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K6" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>151099220740</v>
+        <v>153363000000</v>
       </c>
       <c r="P6" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성 네트워크 관련주로 언급되며, 대장주로서의 가능성과 함께 주가 상승에 대한 기대감 표출.</t>
+          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['광통신', '위성네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>830</v>
+        <v>868</v>
       </c>
       <c r="H7" t="n">
         <v>1.29</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9930</v>
+        <v>8200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.00%</t>
+          <t>+6.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="H8" t="n">
-        <v>4.49</v>
+        <v>0.52</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9280</v>
+        <v>7690</v>
       </c>
       <c r="K8" t="n">
-        <v>10030</v>
+        <v>7670</v>
       </c>
       <c r="L8" t="n">
-        <v>10880</v>
+        <v>9170</v>
       </c>
       <c r="M8" t="n">
-        <v>9800</v>
+        <v>7450</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>0.46</v>
       </c>
       <c r="O8" t="n">
-        <v>20855860050</v>
+        <v>78215195460</v>
       </c>
       <c r="P8" t="n">
-        <v>15640</v>
+        <v>9170</v>
       </c>
       <c r="Q8" t="n">
-        <v>5470</v>
+        <v>3720</v>
       </c>
       <c r="R8" t="n">
-        <v>-88000</v>
+        <v>-24000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>594억 규모 공급 계약 체결로 인한 급등세 및 품절주 특성 분석. 10배 상승 기대와 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['공급 계약', '품절주', '텐버거']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,82 +1195,82 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1927</v>
+        <v>3940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>+3.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.32</v>
+        <v>-0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1901</v>
+        <v>3810</v>
       </c>
       <c r="K9" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1909</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>40028440372</v>
+        <v>88396000000</v>
       </c>
       <c r="P9" t="n">
-        <v>4795</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1524</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-211000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승 관련 전쟁 테마주로 분류되며, 장금상선과의 연관성 언급. 외인 매수세 유입.</t>
+          <t>6G 통신 개발 및 광통신 대세에 따른 수혜 기대감. 긍정적 주가 흐름 예상 및 매수 권유. 장난질 심하다는 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전쟁테마주', '유가상승', '외인매수']</t>
+          <t>['6G 통신', '광통신', '주가 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19600</v>
+        <v>1916</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>465</v>
+        <v>213</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>1901</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1909</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>91649000000</v>
+        <v>40318809871</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R10" t="n">
-        <v>-233000</v>
+        <v>-591000</v>
       </c>
       <c r="S10" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 독려를 통한 공매도 세력에 대한 주주들의 저항 의지 표출. 원전 투자 등 호재 언급.</t>
+          <t>홍해 사태로 인한 해운주 테마 상승 기대감. 국제유가 상승 및 VLCC 용선료 폭등으로 흥아해운 및 장금상선에 대한 긍정적 전망 제시. 외인 매수 전환 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전투자']</t>
+          <t>['홍해 사태', '국제유가', 'VLCC']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>-0.44</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H11" t="n">
         <v>2.92</v>
@@ -1438,7 +1438,7 @@
         <v>3.36</v>
       </c>
       <c r="O11" t="n">
-        <v>90972000000</v>
+        <v>91906000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,10 +1447,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89900</v>
+        <v>415500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>213</v>
+        <v>97</v>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>827</v>
+        <v>244</v>
       </c>
       <c r="H12" t="n">
-        <v>23.59</v>
+        <v>38.02</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89900</v>
+        <v>417500</v>
       </c>
       <c r="K12" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>23.65</v>
+        <v>37.82</v>
       </c>
       <c r="O12" t="n">
-        <v>139933804150</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>아틀라스 관절 부품 전량 수주 및 미래차·로봇 신기술 공개. 유럽·중국차 관세 이슈 및 대규모 수주 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['수주', '미래차', '로봇']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>415500</v>
+        <v>50400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>571</v>
       </c>
       <c r="H13" t="n">
-        <v>38.02</v>
+        <v>38.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>417500</v>
+        <v>50800</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>37.82</v>
+        <v>38.69</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1631,27 +1631,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>13000</v>
+        <v>-134000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>현대모비스의 자동차 부품을 넘어 로봇 사업 확장 및 관절 부품 수주 소식, 미래차 및 로봇 신기술 공개로 인한 성장 전망.</t>
+          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇', '관절부품', '미래차']</t>
+          <t>['수주', '공시', '대규모']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50400</v>
+        <v>29550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>555</v>
+        <v>146</v>
       </c>
       <c r="H14" t="n">
-        <v>38.78</v>
+        <v>25.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50800</v>
+        <v>29800</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>38.69</v>
+        <v>24.99</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1723,67 +1723,67 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-134000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시로 인한 긍정적 시장 반응 및 상승 추세 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '공시', '추세']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29550</v>
+        <v>19550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>144</v>
+        <v>471</v>
       </c>
       <c r="H15" t="n">
-        <v>25.55</v>
+        <v>10.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29800</v>
+        <v>19750</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>19840</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>19060</v>
       </c>
       <c r="N15" t="n">
-        <v>24.99</v>
+        <v>10.64</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>93072160015</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>265000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['대차 해지', '공매도', '원전 투자']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8810</v>
+        <v>8800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
         <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H16" t="n">
         <v>27.19</v>
@@ -1898,7 +1898,7 @@
         <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>15810632395</v>
+        <v>16041845975</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,23 +1907,23 @@
         <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>회사의 경영 실적 악화 및 주가 부진에 대한 불만 고조. 기술적 반등 기대감도 낮음.</t>
+          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['경영 실적', '주가 부진', '기술적 반등']</t>
+          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>192700</v>
+        <v>89900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
-        <v>145</v>
+        <v>828</v>
       </c>
       <c r="H17" t="n">
-        <v>75.98999999999999</v>
+        <v>23.59</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>197500</v>
+        <v>91700</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>75.92</v>
+        <v>23.65</v>
       </c>
       <c r="O17" t="n">
-        <v>410040000000</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,27 +1999,27 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-123000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대형 증권사들의 매도세와 주가 하락에 대한 불만, 배당금 관련 논의.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['우선주', '매도세', '배당금']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14120</v>
+        <v>192800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>562</v>
+        <v>145</v>
       </c>
       <c r="H18" t="n">
-        <v>5.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14600</v>
+        <v>197500</v>
       </c>
       <c r="K18" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.09</v>
+        <v>75.92</v>
       </c>
       <c r="O18" t="n">
-        <v>92807760250</v>
+        <v>415364000000</v>
       </c>
       <c r="P18" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-852000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원전 관련 섹터 상승 기대감 및 공매도 세력과의 갈등 양상. 모건 증권의 대량 매도 물량 출회.</t>
+          <t>대형 증권사들의 매도세와 주가 하락에 대한 불만, 배당금 관련 논의.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '모건 증권']</t>
+          <t>['우선주', '매도세', '배당금']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7410</v>
+        <v>7430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.26%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F19" t="n">
         <v>62</v>
       </c>
       <c r="G19" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="H19" t="n">
         <v>11.72</v>
@@ -2174,7 +2174,7 @@
         <v>11.62</v>
       </c>
       <c r="O19" t="n">
-        <v>9225518945</v>
+        <v>9405104285</v>
       </c>
       <c r="P19" t="n">
         <v>8850</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>금호타이어의 주가 상승 저해 요인 및 기관 매수세 가능성 언급. 삼전닉스의 부지 요구 관련 내용 포함. 공매도 단가 상승 및 주가 흐름에 대한 분석.</t>
+          <t>주가 상승 저해 요인 분석 및 공매도 관련 언급. 지루한 공방전 속 약세 흐름 지속.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가흐름']</t>
+          <t>['공매도', '대차', '주가흐름']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12170</v>
+        <v>1782000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>-0.12</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>450</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>1591</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9399999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>12630</v>
+        <v>1853000</v>
       </c>
       <c r="K20" t="n">
-        <v>12520</v>
+        <v>1773000</v>
       </c>
       <c r="L20" t="n">
-        <v>12930</v>
+        <v>1795000</v>
       </c>
       <c r="M20" t="n">
-        <v>12010</v>
+        <v>1768000</v>
       </c>
       <c r="N20" t="n">
-        <v>0.14</v>
+        <v>50.67</v>
       </c>
       <c r="O20" t="n">
-        <v>59561587850</v>
+        <v>2984995936500</v>
       </c>
       <c r="P20" t="n">
-        <v>20850</v>
+        <v>2987000</v>
       </c>
       <c r="Q20" t="n">
-        <v>4020</v>
+        <v>305500</v>
       </c>
       <c r="R20" t="n">
-        <v>-69000</v>
+        <v>-249000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>가스터빈 관련주로 언급되나, 공급 과잉 우려와 함께 계단식 하락 및 악질적 주가 흐름에 대한 부정적 평가.</t>
+          <t>CPI 발표 및 금리 변동성에 따른 혼조세. 개인 투자자 매수세와 향후 하락 가능성 전망 상존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스터빈', '공급과잉', '계단식하락']</t>
+          <t>['CPI', '금리', '박스권']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1780000</v>
+        <v>14030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-3.90%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>448</v>
+        <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>1601</v>
+        <v>567</v>
       </c>
       <c r="H22" t="n">
-        <v>50.55</v>
+        <v>5.98</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1853000</v>
+        <v>14600</v>
       </c>
       <c r="K22" t="n">
-        <v>1773000</v>
+        <v>14800</v>
       </c>
       <c r="L22" t="n">
-        <v>1795000</v>
+        <v>14950</v>
       </c>
       <c r="M22" t="n">
-        <v>1768000</v>
+        <v>14020</v>
       </c>
       <c r="N22" t="n">
-        <v>50.67</v>
+        <v>6.09</v>
       </c>
       <c r="O22" t="n">
-        <v>2918109373500</v>
+        <v>96266300090</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>30200</v>
       </c>
       <c r="Q22" t="n">
-        <v>305500</v>
+        <v>3540</v>
       </c>
       <c r="R22" t="n">
-        <v>-249000</v>
+        <v>-371000</v>
       </c>
       <c r="S22" t="n">
-        <v>-102000</v>
+        <v>-69000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>CPI 발표 및 금리 변동성에 따른 불확실성 언급, 주가 박스권 흐름에 대한 답답함과 향후 하락 가능성 제기.</t>
+          <t>원전 섹터 관련 언급 속 부정적 전망 및 매도 신호 감지. 단기 과열 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['CPI', '금리', '박스권']</t>
+          <t>['원전', '단기과열', '매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>257750</v>
+        <v>14150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F23" t="n">
-        <v>509</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>1706</v>
+        <v>275</v>
       </c>
       <c r="H23" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>269500</v>
+        <v>14740</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N23" t="n">
-        <v>46.81</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>2313775000000</v>
+        <v>56251533610</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>-1232000</v>
+        <v>-128000</v>
       </c>
       <c r="S23" t="n">
-        <v>-646000</v>
+        <v>-6000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 증권사 리포트 관련 부정적 언급, 반도체 업황 부진과 주가 하락에 대한 불만.</t>
+          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['정치이슈', '반도체', '주가하락']</t>
+          <t>['외국인 매수', '기술적 상승', '목표가']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,46 +2580,46 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14180</v>
+        <v>258000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.21%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>508</v>
       </c>
       <c r="G24" t="n">
-        <v>273</v>
+        <v>1718</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>46.71</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14960</v>
+        <v>269500</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.89</v>
+        <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>55621000000</v>
+        <v>2339921000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2643,27 +2643,27 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-128000</v>
+        <v>-1232000</v>
       </c>
       <c r="S24" t="n">
-        <v>-6000</v>
+        <v>-646000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
+          <t>이재명 관련 정치 이슈와 연계된 부정적 언급 다수. 반도체 수출 최대치에도 불구하고 주가 하락에 대한 불만 표출. 골드만삭스 리포트 관련 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['외국인 매수', '기술적 상승', '목표가']</t>
+          <t>['이재명', '반도체 수출', '골드만삭스']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3555</v>
+        <v>12060</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-8.02%</t>
+          <t>-4.51%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H25" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,183 +2711,183 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3865</v>
+        <v>12630</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>12520</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>12930</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>12010</v>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>0.14</v>
       </c>
       <c r="O25" t="n">
-        <v>41172000000</v>
+        <v>61045515295</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>20850</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4020</v>
       </c>
       <c r="R25" t="n">
-        <v>64000</v>
+        <v>-69000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원전 테마 수급 쏠림 속 부진한 주가 흐름 및 매도 의견 다수. 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전', '테마', '거래량']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>232500</v>
+        <v>9280</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>228</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>828</v>
+        <v>317</v>
       </c>
       <c r="H26" t="n">
-        <v>7.58</v>
+        <v>4.49</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>253000</v>
+        <v>9800</v>
       </c>
       <c r="K26" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8.539999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="O26" t="n">
-        <v>174705937750</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-298000</v>
+        <v>-88000</v>
       </c>
       <c r="S26" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비판과 함께 주가 하락에 대한 불만 표출, 회사 차원의 매수 소각 및 무증 발표 촉구.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['공매도', '주가하락', '기관매수']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26450</v>
+        <v>3640</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-12.71%</t>
+          <t>-5.82%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>461</v>
+        <v>130</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32</v>
+        <v>0.73</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>30300</v>
+        <v>3865</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.33</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>313980000000</v>
+        <v>44240000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2919,34 +2919,218 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>급등주로서의 가능성과 함께 외인 유입 언급, 그러나 종가 하락 마감하며 불확실성 존재.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>['폭락', '주주', '전망']</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>067290</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>232000</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-8.30%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E28" t="n">
+        <v>232</v>
+      </c>
+      <c r="F28" t="n">
+        <v>113</v>
+      </c>
+      <c r="G28" t="n">
+        <v>836</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>253000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>241000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>231000</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="O28" t="n">
+        <v>175749312500</v>
+      </c>
+      <c r="P28" t="n">
+        <v>426000</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>86100</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-298000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-18000</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>공매도 세력에 대한 강한 비판과 함께 주가 하락에 대한 불만 표출, 회사 차원의 매수 소각 및 무증 발표 촉구.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>['공매도', '주가하락', '기관매수']</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>042700</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26500</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-12.54%</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>289</v>
+      </c>
+      <c r="F29" t="n">
+        <v>141</v>
+      </c>
+      <c r="G29" t="n">
+        <v>466</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>30300</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>316126000000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>급등주로서의 가능성과 함께 외인 유입 언급, 그러나 종가 하락 마감하며 불확실성 존재.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
         <v>0.1</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>['급등주', '외인유입', '종가하락']</t>
         </is>
       </c>
-      <c r="X27" t="n">
+      <c r="X29" t="n">
         <v>6</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>386380</t>
         </is>

--- a/data/trending_integrated_20260911_13.xlsx
+++ b/data/trending_integrated_20260911_13.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207656301485</v>
+        <v>207766000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-71000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 테마 부각. 엑스게이트의 양자보안 관련 독점적 지위 강조. 594억 공급계약 및 모건스텐리 대량 매집 공시 기반 상승 전망.</t>
+          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 강한 상승 모멘텀. 594억 공급 계약 및 모건스탠리 매집 공시 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
+          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15370</v>
+        <v>2550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.13%</t>
+          <t>+19.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>376</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>854</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
-        <v>3.14</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>2135</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>190397000000</v>
+        <v>95893000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,27 +711,27 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-359000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
+          <t>미국 정부 양자컴퓨터 보조금 지원 체결 및 모건스탠리 매집 공시 기반으로 한 상승 기대감. 단기 급등 후 변동성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['국제유가', '전쟁 테마', 'WTI']</t>
+          <t>['양자컴퓨터', '공급계약', '모건스탠리']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2540</v>
+        <v>136100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.53%</t>
+          <t>+17.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>116300</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>95411681247</v>
+        <v>454334000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1884000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 정부 양자컴퓨터 보조금 지원 및 공급 계약 체결 사실 기반 상승 기대. 모건스텐리 대량 매집 공시 확인. 양자보안 테마 대장주로서의 강점 부각.</t>
+          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '공급 계약', '모건스텐리']</t>
+          <t>['공급 부족', '3상', '애플']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>136300</v>
+        <v>7440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.20%</t>
+          <t>+13.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>2.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>116300</v>
+        <v>6570</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>450769000000</v>
+        <v>156240000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>52000</v>
+        <v>141000</v>
       </c>
       <c r="S5" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
+          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공급 부족', '3상', '애플']</t>
+          <t>['광통신', '위성네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,46 +924,46 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7490</v>
+        <v>1914</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.00%</t>
+          <t>+8.75%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>324</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6570</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>153363000000</v>
+        <v>40623000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -987,23 +987,23 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-591000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
+          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주로 부각되며 단기 상승 기대감 형성. VLCC 부유식 저장고 용선료 폭등 소식.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '공매도']</t>
+          <t>['홍해 사태', '전쟁 테마주', '유가 상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8300</v>
+        <v>10070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+8.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>868</v>
+        <v>319</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>4.49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>9280</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>4.42</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>21263439475</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R7" t="n">
-        <v>-12000</v>
+        <v>-88000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세계폐암학회(WCLC)에서의 데이터 발표 및 빅파마와의 기술 수출 가능성 언급, 인류 혁명적인 텐버거 주식으로서의 기대감.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상시험', '기술수출', '폐암학회']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8200</v>
+        <v>15390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.63%</t>
+          <t>+6.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.06</v>
+        <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="G8" t="n">
-        <v>83</v>
+        <v>865</v>
       </c>
       <c r="H8" t="n">
-        <v>0.52</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7690</v>
+        <v>14510</v>
       </c>
       <c r="K8" t="n">
-        <v>7670</v>
+        <v>17010</v>
       </c>
       <c r="L8" t="n">
-        <v>9170</v>
+        <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>7450</v>
+        <v>15290</v>
       </c>
       <c r="N8" t="n">
-        <v>0.46</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>78215195460</v>
+        <v>191790998385</v>
       </c>
       <c r="P8" t="n">
-        <v>9170</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3720</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>-24000</v>
+        <v>-359000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>594억 규모 공급 계약 체결로 인한 급등세 및 품절주 특성 분석. 10배 상승 기대와 매도 의견 상존.</t>
+          <t>중동 전쟁 발발 및 국제유가 급등에 따른 전쟁 테마주로서 급등. WTI 100달러 돌파 및 후티 반군 관련 뉴스 기반 상승 기대감. 3연상 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공급 계약', '품절주', '텐버거']</t>
+          <t>['국제유가', '전쟁 테마', 'WTI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3940</v>
+        <v>8100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.53</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3810</v>
+        <v>7990</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>0.46</v>
       </c>
       <c r="O9" t="n">
-        <v>88396000000</v>
+        <v>80691000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1263,27 +1263,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-211000</v>
+        <v>-24000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6G 통신 개발 및 광통신 대세에 따른 수혜 기대감. 긍정적 주가 흐름 예상 및 매수 권유. 장난질 심하다는 언급.</t>
+          <t>품절주 및 텐배거 기대감으로 인한 상승 언급. 포스코 지정 가공센터로서 원재료 공급 사실.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['6G 통신', '광통신', '주가 전망']</t>
+          <t>['품절주', '텐배거', '포스코']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1916</v>
+        <v>26400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>290</v>
+      </c>
+      <c r="F10" t="n">
+        <v>142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>468</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.32</v>
       </c>
-      <c r="E10" t="n">
-        <v>114</v>
-      </c>
-      <c r="F10" t="n">
-        <v>59</v>
-      </c>
-      <c r="G10" t="n">
-        <v>213</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.44</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1901</v>
+        <v>26100</v>
       </c>
       <c r="K10" t="n">
-        <v>2050</v>
+        <v>26350</v>
       </c>
       <c r="L10" t="n">
-        <v>2080</v>
+        <v>30300</v>
       </c>
       <c r="M10" t="n">
-        <v>1909</v>
+        <v>25400</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>40318809871</v>
+        <v>318726240350</v>
       </c>
       <c r="P10" t="n">
-        <v>4795</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1524</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-591000</v>
+        <v>7000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>홍해 사태로 인한 해운주 테마 상승 기대감. 국제유가 상승 및 VLCC 용선료 폭등으로 흥아해운 및 장금상선에 대한 긍정적 전망 제시. 외인 매수 전환 확인.</t>
+          <t>종목에 대한 긍정적, 부정적 의견 혼재. 외인 유입 언급 있으나 하락 마감. 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['홍해 사태', '국제유가', 'VLCC']</t>
+          <t>['외인 유입', '종목 토론']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53200</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.44</v>
+        <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="G11" t="n">
-        <v>143</v>
+        <v>841</v>
       </c>
       <c r="H11" t="n">
-        <v>2.92</v>
+        <v>7.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>53200</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.36</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>91906000000</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-298000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>반도체 수출 호조에도 불구하고 공매도 세력의 압박과 주가 하락에 대한 불만 표출. 기관 매수세 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['반도체수출', '공매도', '기관매수']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>415500</v>
+        <v>19600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+0.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>244</v>
+        <v>473</v>
       </c>
       <c r="H12" t="n">
-        <v>38.02</v>
+        <v>10.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>417500</v>
+        <v>19450</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>37.82</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>94437000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1539,27 +1539,27 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>13000</v>
+        <v>-233000</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>-16000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>아틀라스 관절 부품 전량 수주 및 미래차·로봇 신기술 공개. 유럽·중국차 관세 이슈 및 대규모 수주 기대.</t>
+          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '미래차', '로봇']</t>
+          <t>['대차 해지', '공매도', '원전 투자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50400</v>
+        <v>90200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>571</v>
+        <v>838</v>
       </c>
       <c r="H13" t="n">
-        <v>38.78</v>
+        <v>23.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50800</v>
+        <v>89900</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N13" t="n">
-        <v>38.69</v>
+        <v>23.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>144942354950</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-134000</v>
+        <v>-264000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>26000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
+          <t>미국 투자 협상 및 중동 에너지 공급망 이슈 관련 긍정적 뉴스 언급. 수주 잔고 증가 및 원전 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '공시', '대규모']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29550</v>
+        <v>53300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H14" t="n">
-        <v>25.55</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29800</v>
+        <v>53200</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>24.99</v>
+        <v>3.36</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>92667000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1723,14 +1723,14 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19550</v>
+        <v>3920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.53</v>
       </c>
       <c r="E15" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>471</v>
+        <v>183</v>
       </c>
       <c r="H15" t="n">
-        <v>10.65</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19750</v>
+        <v>3925</v>
       </c>
       <c r="K15" t="n">
-        <v>19500</v>
+        <v>3810</v>
       </c>
       <c r="L15" t="n">
-        <v>19840</v>
+        <v>4180</v>
       </c>
       <c r="M15" t="n">
-        <v>19060</v>
+        <v>3760</v>
       </c>
       <c r="N15" t="n">
-        <v>10.64</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>93072160015</v>
+        <v>89453342544</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-211000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
+          <t>6G 통신 관련 기대감 있으나, 주가 움직임은 지지부진. 뉴스 부재 및 장난질에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '원전 투자']</t>
+          <t>['6G 통신', '광통신', '주가 부진']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8800</v>
+        <v>414500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.90%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H16" t="n">
-        <v>27.19</v>
+        <v>38.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8970</v>
+        <v>415500</v>
       </c>
       <c r="K16" t="n">
-        <v>8780</v>
+        <v>407000</v>
       </c>
       <c r="L16" t="n">
-        <v>8880</v>
+        <v>418000</v>
       </c>
       <c r="M16" t="n">
-        <v>8680</v>
+        <v>404000</v>
       </c>
       <c r="N16" t="n">
-        <v>27.16</v>
+        <v>37.82</v>
       </c>
       <c r="O16" t="n">
-        <v>16041845975</v>
+        <v>52006138250</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>822000</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>283000</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
+          <t>아틀라스 관절부품 전량 수주, 미래 기술 공개 등 사업 확장 뉴스 기반 긍정적 전망. 대차상환 및 순매수 동향 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
+          <t>['수주', '미래 기술', '관절부품']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>213</v>
+        <v>152</v>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>828</v>
+        <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>91700</v>
+        <v>50800</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1999,27 +1999,27 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['수주', '공시', '대규모']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>192800</v>
+        <v>29550</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H18" t="n">
-        <v>75.98999999999999</v>
+        <v>25.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>197500</v>
+        <v>29800</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>75.92</v>
+        <v>24.99</v>
       </c>
       <c r="O18" t="n">
-        <v>415364000000</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2091,119 +2091,119 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-852000</v>
+        <v>265000</v>
       </c>
       <c r="S18" t="n">
-        <v>-123000</v>
+        <v>-69000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대형 증권사들의 매도세와 주가 하락에 대한 불만, 배당금 관련 논의.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['우선주', '매도세', '배당금']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7430</v>
+        <v>8220</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.26%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E19" t="n">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="G19" t="n">
-        <v>409</v>
+        <v>948</v>
       </c>
       <c r="H19" t="n">
-        <v>11.72</v>
+        <v>1.29</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7680</v>
+        <v>8300</v>
       </c>
       <c r="K19" t="n">
+        <v>8400</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8700</v>
+      </c>
+      <c r="M19" t="n">
         <v>7540</v>
       </c>
-      <c r="L19" t="n">
-        <v>7660</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7360</v>
-      </c>
       <c r="N19" t="n">
-        <v>11.62</v>
+        <v>1.17</v>
       </c>
       <c r="O19" t="n">
-        <v>9405104285</v>
+        <v>23287298185</v>
       </c>
       <c r="P19" t="n">
-        <v>8850</v>
+        <v>21500</v>
       </c>
       <c r="Q19" t="n">
-        <v>4220</v>
+        <v>2300</v>
       </c>
       <c r="R19" t="n">
-        <v>43000</v>
+        <v>-12000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 상승 저해 요인 분석 및 공매도 관련 언급. 지루한 공방전 속 약세 흐름 지속.</t>
+          <t>WCLC 학회 발표 및 기술 수출 가능성에 대한 높은 기대감 표출. 글로벌 빅파마 협력 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '주가흐름']</t>
+          <t>['WCLC', '폐암학회', '기술 수출']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,130 +2212,130 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1782000</v>
+        <v>3565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.12</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>450</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>1591</v>
+        <v>135</v>
       </c>
       <c r="H20" t="n">
-        <v>50.55</v>
+        <v>0.73</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1853000</v>
+        <v>3620</v>
       </c>
       <c r="K20" t="n">
-        <v>1773000</v>
+        <v>3725</v>
       </c>
       <c r="L20" t="n">
-        <v>1795000</v>
+        <v>3915</v>
       </c>
       <c r="M20" t="n">
-        <v>1768000</v>
+        <v>3520</v>
       </c>
       <c r="N20" t="n">
-        <v>50.67</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>2984995936500</v>
+        <v>45621094294</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>4335</v>
       </c>
       <c r="Q20" t="n">
-        <v>305500</v>
+        <v>1246</v>
       </c>
       <c r="R20" t="n">
-        <v>-249000</v>
+        <v>64000</v>
       </c>
       <c r="S20" t="n">
-        <v>-102000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>CPI 발표 및 금리 변동성에 따른 혼조세. 개인 투자자 매수세와 향후 하락 가능성 전망 상존.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['CPI', '금리', '박스권']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15040</v>
+        <v>8810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>27.19</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15640</v>
+        <v>8950</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>16247000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,211 +2367,211 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>22000</v>
+        <v>-100000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14030</v>
+        <v>14680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>567</v>
+        <v>256</v>
       </c>
       <c r="H22" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14600</v>
+        <v>15040</v>
       </c>
       <c r="K22" t="n">
-        <v>14800</v>
+        <v>14550</v>
       </c>
       <c r="L22" t="n">
-        <v>14950</v>
+        <v>15260</v>
       </c>
       <c r="M22" t="n">
-        <v>14020</v>
+        <v>14350</v>
       </c>
       <c r="N22" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>96266300090</v>
+        <v>19323694540</v>
       </c>
       <c r="P22" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q22" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R22" t="n">
-        <v>-371000</v>
+        <v>22000</v>
       </c>
       <c r="S22" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 섹터 관련 언급 속 부정적 전망 및 매도 신호 감지. 단기 과열 및 주가 하락 우려.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '단기과열', '매도']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14150</v>
+        <v>192400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-2.58%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>275</v>
+        <v>146</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14740</v>
+        <v>197500</v>
       </c>
       <c r="K23" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>14560</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>14030</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>75.92</v>
       </c>
       <c r="O23" t="n">
-        <v>56251533610</v>
+        <v>423161000000</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-128000</v>
+        <v>-852000</v>
       </c>
       <c r="S23" t="n">
-        <v>-6000</v>
+        <v>-123000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 기술적 상승 기대감. 높은 목표가 설정 및 신중론 혼재.</t>
+          <t>기관 및 외국인 매도세에 대한 불만과 하락에 대한 부정적 언급. 특별 배당 기대감 있으나 불확실성 존재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['외국인 매수', '기술적 상승', '목표가']</t>
+          <t>['기관 매도', '외국인 매도', '특별 배당']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>258000</v>
+        <v>7430</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-3.26%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>129</v>
       </c>
       <c r="F24" t="n">
-        <v>508</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
-        <v>1718</v>
+        <v>430</v>
       </c>
       <c r="H24" t="n">
-        <v>46.71</v>
+        <v>11.72</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,51 +2619,51 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>269500</v>
+        <v>7680</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>7660</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="N24" t="n">
-        <v>46.81</v>
+        <v>11.62</v>
       </c>
       <c r="O24" t="n">
-        <v>2339921000000</v>
+        <v>9642085155</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4220</v>
       </c>
       <c r="R24" t="n">
-        <v>-1232000</v>
+        <v>43000</v>
       </c>
       <c r="S24" t="n">
-        <v>-646000</v>
+        <v>-2000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>이재명 관련 정치 이슈와 연계된 부정적 언급 다수. 반도체 수출 최대치에도 불구하고 주가 하락에 대한 불만 표출. 골드만삭스 리포트 관련 언급.</t>
+          <t>주가 상승에 대한 기대감과 함께 특정 창구 매매 동향 언급. 광주 반도체 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['이재명', '반도체 수출', '골드만삭스']</t>
+          <t>['광주반도체', '주가', '매매동향']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,90 +2672,90 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12060</v>
+        <v>1786000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.51%</t>
+          <t>-3.62%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>-0.12</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>51</v>
+        <v>451</v>
       </c>
       <c r="G25" t="n">
-        <v>88</v>
+        <v>1622</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12630</v>
+        <v>1853000</v>
       </c>
       <c r="K25" t="n">
-        <v>12520</v>
+        <v>1773000</v>
       </c>
       <c r="L25" t="n">
-        <v>12930</v>
+        <v>1795000</v>
       </c>
       <c r="M25" t="n">
-        <v>12010</v>
+        <v>1768000</v>
       </c>
       <c r="N25" t="n">
-        <v>0.14</v>
+        <v>50.67</v>
       </c>
       <c r="O25" t="n">
-        <v>61045515295</v>
+        <v>3049535883000</v>
       </c>
       <c r="P25" t="n">
-        <v>20850</v>
+        <v>2987000</v>
       </c>
       <c r="Q25" t="n">
-        <v>4020</v>
+        <v>305500</v>
       </c>
       <c r="R25" t="n">
-        <v>-69000</v>
+        <v>-249000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>원전 테마 수급 쏠림 속 부진한 주가 흐름 및 매도 의견 다수. 상폐 가능성 언급.</t>
+          <t>CPI 발표 및 금리 변동성에 따른 혼조세. 개인 투자자 매수세와 향후 하락 가능성 전망 상존.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['원전', '테마', '거래량']</t>
+          <t>['CPI', '금리', '박스권']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9280</v>
+        <v>14050</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>317</v>
+        <v>593</v>
       </c>
       <c r="H26" t="n">
-        <v>4.49</v>
+        <v>5.98</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,91 +2803,91 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>9800</v>
+        <v>14600</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>14950</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>14020</v>
       </c>
       <c r="N26" t="n">
-        <v>4.42</v>
+        <v>6.09</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>98430012035</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R26" t="n">
-        <v>-88000</v>
+        <v>-371000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>원전 섹터 테마와 관련하여 자포리 원전 이슈 언급. 모건스탠리의 대규모 매도세로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['원전 섹터', '자포리 원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3640</v>
+        <v>14140</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E27" t="n">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>130</v>
+        <v>293</v>
       </c>
       <c r="H27" t="n">
-        <v>0.73</v>
+        <v>2.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,91 +2895,91 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3865</v>
+        <v>14740</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N27" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="O27" t="n">
-        <v>44240000000</v>
+        <v>56994989250</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-128000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>외국인 매수세와 함께 상승 기대감 표출. 오라클 순익 급증 뉴스 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['오라클', '외국인', '상승']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>232000</v>
+        <v>258000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-8.30%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.96</v>
+        <v>-0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>232</v>
+        <v>800</v>
       </c>
       <c r="F28" t="n">
-        <v>113</v>
+        <v>509</v>
       </c>
       <c r="G28" t="n">
-        <v>836</v>
+        <v>1756</v>
       </c>
       <c r="H28" t="n">
-        <v>7.58</v>
+        <v>46.71</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,51 +2987,51 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>253000</v>
+        <v>269500</v>
       </c>
       <c r="K28" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>8.539999999999999</v>
+        <v>46.81</v>
       </c>
       <c r="O28" t="n">
-        <v>175749312500</v>
+        <v>2371064000000</v>
       </c>
       <c r="P28" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-298000</v>
+        <v>-1232000</v>
       </c>
       <c r="S28" t="n">
-        <v>-18000</v>
+        <v>-646000</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비판과 함께 주가 하락에 대한 불만 표출, 회사 차원의 매수 소각 및 무증 발표 촉구.</t>
+          <t>정치적 이슈와 연관된 언급 다수, 네이버 증권의 불편함 지적. 반도체 수출 호조에도 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['공매도', '주가하락', '기관매수']</t>
+          <t>['이재명', '반도체 수출', '주가 하락']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,38 +3040,38 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26500</v>
+        <v>12150</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-12.54%</t>
+          <t>-6.75%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
-        <v>289</v>
+        <v>91</v>
       </c>
       <c r="F29" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>466</v>
+        <v>95</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>30300</v>
+        <v>13030</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="O29" t="n">
-        <v>316126000000</v>
+        <v>61544000000</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3103,27 +3103,27 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>7000</v>
+        <v>-69000</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>급등주로서의 가능성과 함께 외인 유입 언급, 그러나 종가 하락 마감하며 불확실성 존재.</t>
+          <t>계단식 하락 및 악질적인 주가 움직임에 대한 불만. 원전 테마로 수급 쏠림 현상 관찰.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['급등주', '외인유입', '종가하락']</t>
+          <t>['계단식 하락', '품절주', '원전 테마']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_13.xlsx
+++ b/data/trending_integrated_20260911_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12610</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207766000000</v>
+        <v>207892447725</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
         <v>-71000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목에 따른 강한 상승 모멘텀. 594억 공급 계약 및 모건스탠리 매집 공시 확인.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 관련주 부각. 594억 공급 계약 및 모건스텐리 매집 공시 확인. 양자+보안 유일 대장주로서 강한 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
+          <t>['사이버 보안', '젠슨 황', '공급 계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2550</v>
+        <v>2615</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+19.44%</t>
+          <t>+22.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H3" t="n">
         <v>3.83</v>
@@ -702,7 +702,7 @@
         <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>95893000000</v>
+        <v>99726000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,23 +711,23 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-2091000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 정부 양자컴퓨터 보조금 지원 체결 및 모건스탠리 매집 공시 기반으로 한 상승 기대감. 단기 급등 후 변동성.</t>
+          <t>미국 정부 양자컴퓨터 보조금 지원 및 공급 계약 체결 사실 언급. 모건스텐리의 48만주 매집 공시 확인. 양자컴퓨터 대장주로서의 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '공급계약', '모건스탠리']</t>
+          <t>['양자컴퓨터', '공급 계약', '모건스텐리']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136100</v>
+        <v>16160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+17.02%</t>
+          <t>+21.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="H4" t="n">
-        <v>4.32</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>116300</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>454334000000</v>
+        <v>124990000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -803,23 +803,23 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
+          <t>상승 추세 지속 및 기관 연속 매집 확인. 아로마티카와 함께 화장품 제조 대장주로서의 기대감 형성. 전고점 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급 부족', '3상', '애플']</t>
+          <t>['상승 추세', '기관 매집', '화장품 제조']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7440</v>
+        <v>137500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.24%</t>
+          <t>+18.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="H5" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6570</v>
+        <v>116300</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>156240000000</v>
+        <v>459933000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,27 +895,27 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>141000</v>
+        <v>39000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
+          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '공매도']</t>
+          <t>['공급 부족', '3상', '애플']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1914</v>
+        <v>7470</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.75%</t>
+          <t>+11.49%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.32</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>332</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1760</v>
+        <v>6700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>40623000000</v>
+        <v>157777381845</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R6" t="n">
-        <v>-591000</v>
+        <v>110000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승에 따른 전쟁 테마주로 부각되며 단기 상승 기대감 형성. VLCC 부유식 저장고 용선료 폭등 소식.</t>
+          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['홍해 사태', '전쟁 테마주', '유가 상승']</t>
+          <t>['광통신', '위성네트워크', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10070</v>
+        <v>9980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.51%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H7" t="n">
         <v>4.49</v>
@@ -1070,7 +1070,7 @@
         <v>4.42</v>
       </c>
       <c r="O7" t="n">
-        <v>21263439475</v>
+        <v>21386179445</v>
       </c>
       <c r="P7" t="n">
         <v>15640</v>
@@ -1079,7 +1079,7 @@
         <v>5470</v>
       </c>
       <c r="R7" t="n">
-        <v>-88000</v>
+        <v>-97000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15390</v>
+        <v>15150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>+4.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F8" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G8" t="n">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="H8" t="n">
         <v>3.14</v>
@@ -1156,13 +1156,13 @@
         <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>15290</v>
+        <v>15100</v>
       </c>
       <c r="N8" t="n">
         <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>191790998385</v>
+        <v>195229539965</v>
       </c>
       <c r="P8" t="n">
         <v>36200</v>
@@ -1171,7 +1171,7 @@
         <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>-359000</v>
+        <v>-386000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1207,39 +1207,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8100</v>
+        <v>19780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>476</v>
       </c>
       <c r="H9" t="n">
-        <v>0.52</v>
+        <v>10.65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7990</v>
+        <v>19450</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.46</v>
+        <v>10.64</v>
       </c>
       <c r="O9" t="n">
-        <v>80691000000</v>
+        <v>98063000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1263,27 +1263,27 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>품절주 및 텐배거 기대감으로 인한 상승 언급. 포스코 지정 가공센터로서 원재료 공급 사실.</t>
+          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['품절주', '텐배거', '포스코']</t>
+          <t>['대차 해지', '공매도', '원전 투자']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26400</v>
+        <v>90600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
-        <v>468</v>
+        <v>848</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>23.59</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26100</v>
+        <v>89900</v>
       </c>
       <c r="K10" t="n">
-        <v>26350</v>
+        <v>88700</v>
       </c>
       <c r="L10" t="n">
-        <v>30300</v>
+        <v>91000</v>
       </c>
       <c r="M10" t="n">
-        <v>25400</v>
+        <v>88000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>23.65</v>
       </c>
       <c r="O10" t="n">
-        <v>318726240350</v>
+        <v>151942645350</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>7000</v>
+        <v>-289000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>종목에 대한 긍정적, 부정적 의견 혼재. 외인 유입 언급 있으나 하락 마감. 명확한 근거 부족.</t>
+          <t>미국 투자 협상 및 중동 에너지 공급망 이슈 관련 긍정적 뉴스 언급. 수주 잔고 증가 및 원전 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인 유입', '종목 토론']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253000</v>
+        <v>1914</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.96</v>
+        <v>0.32</v>
       </c>
       <c r="E11" t="n">
-        <v>232</v>
+        <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>841</v>
+        <v>234</v>
       </c>
       <c r="H11" t="n">
-        <v>7.58</v>
+        <v>2.44</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>1901</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1907</v>
       </c>
       <c r="N11" t="n">
-        <v>8.539999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>41189868896</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>-389000</v>
       </c>
       <c r="S11" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 수출 호조에도 불구하고 공매도 세력의 압박과 주가 하락에 대한 불만 표출. 기관 매수세 언급.</t>
+          <t>홍해 사태 및 유가 상승 관련 전쟁 테마주로 부각되며 단기 급등 기대감 형성. VLCC 용선료 폭등 및 유가 200달러 전망 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체수출', '공매도', '기관매수']</t>
+          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19600</v>
+        <v>53400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>473</v>
+        <v>147</v>
       </c>
       <c r="H12" t="n">
-        <v>10.65</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>19450</v>
+        <v>53200</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>3.36</v>
       </c>
       <c r="O12" t="n">
-        <v>94437000000</v>
+        <v>93373000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1539,119 +1539,119 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-233000</v>
+        <v>128000</v>
       </c>
       <c r="S12" t="n">
-        <v>-16000</v>
+        <v>24000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '원전 투자']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90200</v>
+        <v>7990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>838</v>
+        <v>104</v>
       </c>
       <c r="H13" t="n">
-        <v>23.59</v>
+        <v>0.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>89900</v>
+        <v>7990</v>
       </c>
       <c r="K13" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>23.65</v>
+        <v>0.46</v>
       </c>
       <c r="O13" t="n">
-        <v>144942354950</v>
+        <v>82907000000</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-264000</v>
+        <v>-2000</v>
       </c>
       <c r="S13" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 투자 협상 및 중동 에너지 공급망 이슈 관련 긍정적 뉴스 언급. 수주 잔고 증가 및 원전 사업 수혜 기대.</t>
+          <t>594억 공급 계약 재료와 함께 포스코 지정 가공센터로서의 역할 언급. 품절주 특성 및 신고가 경신에 대한 기대감 형성. 텐배거 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지']</t>
+          <t>['공급 계약', '포스코', '품절주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53300</v>
+        <v>415500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.44</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>147</v>
+        <v>270</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92</v>
+        <v>38.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>53200</v>
+        <v>415500</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.36</v>
+        <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>92667000000</v>
+        <v>53641840000</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>116000</v>
+        <v>23000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,95 +1747,95 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3920</v>
+        <v>50400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.53</v>
+        <v>0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
-        <v>183</v>
+        <v>583</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>38.78</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3925</v>
+        <v>50800</v>
       </c>
       <c r="K15" t="n">
-        <v>3810</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4180</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3760</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>38.69</v>
       </c>
       <c r="O15" t="n">
-        <v>89453342544</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-211000</v>
+        <v>-163000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6G 통신 관련 기대감 있으나, 주가 움직임은 지지부진. 뉴스 부재 및 장난질에 대한 불만.</t>
+          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['6G 통신', '광통신', '주가 부진']</t>
+          <t>['수주', '공시', '대규모']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>414500</v>
+        <v>29550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c r="H16" t="n">
-        <v>38.02</v>
+        <v>25.55</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,143 +1883,143 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>415500</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>37.82</v>
+        <v>24.99</v>
       </c>
       <c r="O16" t="n">
-        <v>52006138250</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>13000</v>
+        <v>410000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-200000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주, 미래 기술 공개 등 사업 확장 뉴스 기반 긍정적 전망. 대차상환 및 순매수 동향 언급.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '미래 기술', '관절부품']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50400</v>
+        <v>3890</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>-0.53</v>
       </c>
       <c r="E17" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>578</v>
+        <v>188</v>
       </c>
       <c r="H17" t="n">
-        <v>38.78</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>50800</v>
+        <v>3925</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
       <c r="N17" t="n">
-        <v>38.69</v>
+        <v>1.57</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>90568837553</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R17" t="n">
-        <v>-134000</v>
+        <v>-582000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
+          <t>6G 통신 관련주로 부각되며 개발 기대감 형성. 젠슨 황 발언 및 데이터센터 6G 연관성 언급. 장난질 심한 움직임에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '공시', '대규모']</t>
+          <t>['6G 통신', '데이터센터', '개발 기대']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29550</v>
+        <v>8840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="H18" t="n">
-        <v>25.55</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,143 +2067,143 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29800</v>
+        <v>8970</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8880</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N18" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>16537536025</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>265000</v>
+        <v>-34000</v>
       </c>
       <c r="S18" t="n">
-        <v>-69000</v>
+        <v>-198000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8220</v>
+        <v>192900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="G19" t="n">
-        <v>948</v>
+        <v>148</v>
       </c>
       <c r="H19" t="n">
-        <v>1.29</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8300</v>
+        <v>197500</v>
       </c>
       <c r="K19" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.17</v>
+        <v>75.92</v>
       </c>
       <c r="O19" t="n">
-        <v>23287298185</v>
+        <v>429194000000</v>
       </c>
       <c r="P19" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-12000</v>
+        <v>-1070000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-84000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>WCLC 학회 발표 및 기술 수출 가능성에 대한 높은 기대감 표출. 글로벌 빅파마 협력 가능성 언급.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['WCLC', '폐암학회', '기술 수출']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3565</v>
+        <v>14120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>135</v>
+        <v>601</v>
       </c>
       <c r="H20" t="n">
-        <v>0.73</v>
+        <v>5.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3620</v>
+        <v>14600</v>
       </c>
       <c r="K20" t="n">
-        <v>3725</v>
+        <v>14800</v>
       </c>
       <c r="L20" t="n">
-        <v>3915</v>
+        <v>14950</v>
       </c>
       <c r="M20" t="n">
-        <v>3520</v>
+        <v>14020</v>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>6.09</v>
       </c>
       <c r="O20" t="n">
-        <v>45621094294</v>
+        <v>99710395820</v>
       </c>
       <c r="P20" t="n">
-        <v>4335</v>
+        <v>30200</v>
       </c>
       <c r="Q20" t="n">
-        <v>1246</v>
+        <v>3540</v>
       </c>
       <c r="R20" t="n">
-        <v>64000</v>
+        <v>-290000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-96000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원전 섹터 테마와 관련하여 자포리 원전 이슈 언급. 모건스탠리의 대규모 매도세로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전 섹터', '자포리 원전', '모건스탠리']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8810</v>
+        <v>1792000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>450</v>
       </c>
       <c r="G21" t="n">
-        <v>268</v>
+        <v>1665</v>
       </c>
       <c r="H21" t="n">
-        <v>27.19</v>
+        <v>50.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8950</v>
+        <v>1853000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N21" t="n">
-        <v>27.16</v>
+        <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>16247000000</v>
+        <v>3130225130000</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R21" t="n">
-        <v>-100000</v>
+        <v>-402000</v>
       </c>
       <c r="S21" t="n">
-        <v>-78000</v>
+        <v>-168000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
+          <t>CPI 발표 및 금리 변동성에 따른 주가 변동성 우려. 다음 주 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
+          <t>['CPI', '금리', '박스권']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14680</v>
+        <v>7420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>256</v>
+        <v>449</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>11.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,143 +2435,143 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15040</v>
+        <v>7680</v>
       </c>
       <c r="K22" t="n">
-        <v>14550</v>
+        <v>7540</v>
       </c>
       <c r="L22" t="n">
-        <v>15260</v>
+        <v>7660</v>
       </c>
       <c r="M22" t="n">
-        <v>14350</v>
+        <v>7360</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>11.62</v>
       </c>
       <c r="O22" t="n">
-        <v>19323694540</v>
+        <v>9832498825</v>
       </c>
       <c r="P22" t="n">
-        <v>19380</v>
+        <v>8850</v>
       </c>
       <c r="Q22" t="n">
-        <v>3200</v>
+        <v>4220</v>
       </c>
       <c r="R22" t="n">
-        <v>22000</v>
+        <v>51000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['반도체', '신영증권', '주가상승']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>192400</v>
+        <v>14190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-3.73%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
-        <v>146</v>
+        <v>306</v>
       </c>
       <c r="H23" t="n">
-        <v>75.98999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>197500</v>
+        <v>14740</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N23" t="n">
-        <v>75.92</v>
+        <v>2.89</v>
       </c>
       <c r="O23" t="n">
-        <v>423161000000</v>
+        <v>57381365965</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>-852000</v>
+        <v>-282000</v>
       </c>
       <c r="S23" t="n">
-        <v>-123000</v>
+        <v>-19000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>기관 및 외국인 매도세에 대한 불만과 하락에 대한 부정적 언급. 특별 배당 기대감 있으나 불확실성 존재.</t>
+          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['기관 매도', '외국인 매도', '특별 배당']</t>
+          <t>['광통신', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7430</v>
+        <v>15040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.26%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="H24" t="n">
-        <v>11.72</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,51 +2619,51 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7680</v>
+        <v>15640</v>
       </c>
       <c r="K24" t="n">
-        <v>7540</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>7660</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>11.62</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>9642085155</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4220</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>43000</v>
+        <v>16000</v>
       </c>
       <c r="S24" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 특정 창구 매매 동향 언급. 광주 반도체 관련 내용 포함.</t>
+          <t>서남권 반도체 클러스터 조기 생산 전망 및 외국인 프로그램 매수세 유입. 건설 부지 추가 확보 검토.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['광주반도체', '주가', '매매동향']</t>
+          <t>['반도체클러스터', '건설', '외국인']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1786000</v>
+        <v>258500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.62%</t>
+          <t>-3.90%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
         <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="G25" t="n">
-        <v>1622</v>
+        <v>1796</v>
       </c>
       <c r="H25" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,51 +2711,51 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1853000</v>
+        <v>269000</v>
       </c>
       <c r="K25" t="n">
-        <v>1773000</v>
+        <v>258000</v>
       </c>
       <c r="L25" t="n">
-        <v>1795000</v>
+        <v>261000</v>
       </c>
       <c r="M25" t="n">
-        <v>1768000</v>
+        <v>256500</v>
       </c>
       <c r="N25" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>3049535883000</v>
+        <v>2435714825000</v>
       </c>
       <c r="P25" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q25" t="n">
-        <v>305500</v>
+        <v>72100</v>
       </c>
       <c r="R25" t="n">
-        <v>-249000</v>
+        <v>-2974000</v>
       </c>
       <c r="S25" t="n">
-        <v>-102000</v>
+        <v>-1056000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>CPI 발표 및 금리 변동성에 따른 혼조세. 개인 투자자 매수세와 향후 하락 가능성 전망 상존.</t>
+          <t>이재명 관련 정치적 이슈와 함께 주가 하락에 대한 불만 표출. 반도체 수출 최대치와 주가 하락 간의 괴리감 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['CPI', '금리', '박스권']</t>
+          <t>['정치 테마주', '반도체', '주가 하락']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14050</v>
+        <v>12100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>-4.20%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.11</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G26" t="n">
-        <v>593</v>
+        <v>96</v>
       </c>
       <c r="H26" t="n">
-        <v>5.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14600</v>
+        <v>12630</v>
       </c>
       <c r="K26" t="n">
-        <v>14800</v>
+        <v>12520</v>
       </c>
       <c r="L26" t="n">
-        <v>14950</v>
+        <v>12930</v>
       </c>
       <c r="M26" t="n">
-        <v>14020</v>
+        <v>12010</v>
       </c>
       <c r="N26" t="n">
-        <v>6.09</v>
+        <v>0.14</v>
       </c>
       <c r="O26" t="n">
-        <v>98430012035</v>
+        <v>61919289430</v>
       </c>
       <c r="P26" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q26" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R26" t="n">
-        <v>-371000</v>
+        <v>-106000</v>
       </c>
       <c r="S26" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>원전 섹터 테마와 관련하여 자포리 원전 이슈 언급. 모건스탠리의 대규모 매도세로 인한 하락 우려.</t>
+          <t>가스터빈 관련주로 언급되나, 수급 쏠림 및 원전 테마주 대비 약세. 계단식 하락 및 거래량 부진으로 인한 약세 전망. 넥스트장 기대감 언급.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['원전 섹터', '자포리 원전', '모건스탠리']</t>
+          <t>['가스터빈', '원전 테마', '거래량 부진']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14140</v>
+        <v>7810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>-5.90%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.39</v>
+        <v>0.12</v>
       </c>
       <c r="E27" t="n">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="G27" t="n">
-        <v>293</v>
+        <v>975</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,51 +2895,51 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>14740</v>
+        <v>8300</v>
       </c>
       <c r="K27" t="n">
-        <v>14050</v>
+        <v>8400</v>
       </c>
       <c r="L27" t="n">
-        <v>14560</v>
+        <v>8700</v>
       </c>
       <c r="M27" t="n">
-        <v>14030</v>
+        <v>7540</v>
       </c>
       <c r="N27" t="n">
-        <v>2.89</v>
+        <v>1.17</v>
       </c>
       <c r="O27" t="n">
-        <v>56994989250</v>
+        <v>27476786640</v>
       </c>
       <c r="P27" t="n">
-        <v>31500</v>
+        <v>21500</v>
       </c>
       <c r="Q27" t="n">
-        <v>1272</v>
+        <v>2300</v>
       </c>
       <c r="R27" t="n">
-        <v>-128000</v>
+        <v>-73000</v>
       </c>
       <c r="S27" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>외국인 매수세와 함께 상승 기대감 표출. 오라클 순익 급증 뉴스 언급.</t>
+          <t>9월 14일 세계폐암학회(WCLC) 센딥파텔 교수 발표 데이터 기반 주가 대폭등 기대. 외국계 증권사 매수 유입.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['오라클', '외국인', '상승']</t>
+          <t>['임상시험', '데이터', '학회']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,46 +2948,46 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>258000</v>
+        <v>3585</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="F28" t="n">
-        <v>509</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>1756</v>
+        <v>134</v>
       </c>
       <c r="H28" t="n">
-        <v>46.71</v>
+        <v>0.73</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>269500</v>
+        <v>3865</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2999,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>46.81</v>
+        <v>1.54</v>
       </c>
       <c r="O28" t="n">
-        <v>2371064000000</v>
+        <v>46066000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3011,119 +3011,119 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-1232000</v>
+        <v>-36000</v>
       </c>
       <c r="S28" t="n">
-        <v>-646000</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 언급 다수, 네이버 증권의 불편함 지적. 반도체 수출 호조에도 주가 하락에 대한 불만.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['이재명', '반도체 수출', '주가 하락']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12150</v>
+        <v>233500</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-6.75%</t>
+          <t>-7.71%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.8</v>
+        <v>-0.96</v>
       </c>
       <c r="E29" t="n">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="F29" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="G29" t="n">
-        <v>95</v>
+        <v>849</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9399999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>13030</v>
+        <v>253000</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N29" t="n">
-        <v>0.14</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>61544000000</v>
+        <v>191585250250</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R29" t="n">
-        <v>-69000</v>
+        <v>-415000</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>계단식 하락 및 악질적인 주가 움직임에 대한 불만. 원전 테마로 수급 쏠림 현상 관찰.</t>
+          <t>9월 TC본더 수출 데이터 관련 공매도 세력의 압박 속 주가 하락. 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['계단식 하락', '품절주', '원전 테마']</t>
+          <t>['TC본더', '수출', '공매도']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3132,7 +3132,99 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>042700</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26350</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-13.04%</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>295</v>
+      </c>
+      <c r="F30" t="n">
+        <v>145</v>
+      </c>
+      <c r="G30" t="n">
+        <v>470</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>30300</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>320183000000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>종목에 대한 긍정적, 부정적 의견 혼재. 외인 유입 언급 있으나 하락 마감. 명확한 근거 부족.</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>['외인 유입', '종목 토론']</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_13.xlsx
+++ b/data/trending_integrated_20260911_13.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207892447725</v>
+        <v>207966000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-71000</v>
@@ -655,39 +655,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2615</v>
+        <v>16310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.48%</t>
+          <t>+22.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>1.24</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2135</v>
+        <v>13340</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="O3" t="n">
-        <v>99726000000</v>
+        <v>131885000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -711,23 +711,23 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-2091000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 정부 양자컴퓨터 보조금 지원 및 공급 계약 체결 사실 언급. 모건스텐리의 48만주 매집 공시 확인. 양자컴퓨터 대장주로서의 기대감 형성.</t>
+          <t>기관 연속 매집 확인에 따른 주가 상승 기대감. 전고점 돌파 및 2만원 이상 상승 전망. 다만, 추격 매수에 대한 경계와 주가 변동성에 대한 언급도 있음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '공급 계약', '모건스텐리']</t>
+          <t>['기관매집', '상승전망', '전고점돌파']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16160</v>
+        <v>2580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.14%</t>
+          <t>+21.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13340</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>124990000000</v>
+        <v>101345230109</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
-        <v>36000</v>
+        <v>-2091000</v>
       </c>
       <c r="S4" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상승 추세 지속 및 기관 연속 매집 확인. 아로마티카와 함께 화장품 제조 대장주로서의 기대감 형성. 전고점 돌파 및 추가 상승 전망.</t>
+          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['상승 추세', '기관 매집', '화장품 제조']</t>
+          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137500</v>
+        <v>139000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.23%</t>
+          <t>+19.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="H5" t="n">
         <v>4.32</v>
@@ -886,7 +886,7 @@
         <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>459933000000</v>
+        <v>467374000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7470</v>
+        <v>7350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.49%</t>
+          <t>+11.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
         <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H6" t="n">
         <v>2.15</v>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K6" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>157777381845</v>
+        <v>160120000000</v>
       </c>
       <c r="P6" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>110000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 분야에서의 대장주 역할 기대. 공매도 세력 이탈 확인 및 매수 기회 포착. 보안 관련 긍정적 언급.</t>
+          <t>KoAct 광통신&amp;위성네트워크액티브 편입 및 대장주로서의 부각. 공매도 세력의 튀는 움직임 확인. 주가 상승에 대한 기대감과 함께 매수 타이밍에 대한 고민 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '공매도']</t>
+          <t>['광통신', '위성네트워크', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9980</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.54%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>322</v>
+        <v>452</v>
       </c>
       <c r="H7" t="n">
-        <v>4.49</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9280</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.42</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>21386179445</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-97000</v>
+        <v>51000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['반도체', '신영증권', '주가상승']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15150</v>
+        <v>14980</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+4.41%</t>
+          <t>+3.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="F8" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G8" t="n">
-        <v>874</v>
+        <v>926</v>
       </c>
       <c r="H8" t="n">
         <v>3.14</v>
@@ -1156,13 +1156,13 @@
         <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>15100</v>
+        <v>14910</v>
       </c>
       <c r="N8" t="n">
         <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>195229539965</v>
+        <v>199279109575</v>
       </c>
       <c r="P8" t="n">
         <v>36200</v>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19780</v>
+        <v>7920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+2.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>476</v>
+        <v>109</v>
       </c>
       <c r="H9" t="n">
-        <v>10.65</v>
+        <v>0.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19450</v>
+        <v>7690</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7670</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>7450</v>
       </c>
       <c r="N9" t="n">
-        <v>10.64</v>
+        <v>0.46</v>
       </c>
       <c r="O9" t="n">
-        <v>98063000000</v>
+        <v>84453932175</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9170</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대차 해지를 통한 공매도 세력에 대한 주주들의 연대 및 행동 촉구. 원전 투자 관련 긍정적 뉴스 언급.</t>
+          <t>금강철강, 594억 공급계약 관련 급등 기대감 및 신고가 경신. 품절주 특성으로 인한 변동성 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '원전 투자']</t>
+          <t>['품절주', '공급계약', '신고가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90600</v>
+        <v>19870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+2.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>848</v>
+        <v>499</v>
       </c>
       <c r="H10" t="n">
-        <v>23.59</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>89900</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>91000</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>23.65</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>151942645350</v>
+        <v>104981000000</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-289000</v>
+        <v>-76000</v>
       </c>
       <c r="S10" t="n">
-        <v>70000</v>
+        <v>-15000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 투자 협상 및 중동 에너지 공급망 이슈 관련 긍정적 뉴스 언급. 수주 잔고 증가 및 원전 사업 수혜 기대.</t>
+          <t>대차 해지 운동 독려 및 공매도 세력과의 전쟁 선포. 원전 8기 대미 투자 관련 뉴스 언급. 목표가 상향 소식과 함께 2만원 이상 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지']</t>
+          <t>['대차해지', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1914</v>
+        <v>26500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>298</v>
+      </c>
+      <c r="F11" t="n">
+        <v>148</v>
+      </c>
+      <c r="G11" t="n">
+        <v>472</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.32</v>
       </c>
-      <c r="E11" t="n">
-        <v>120</v>
-      </c>
-      <c r="F11" t="n">
-        <v>62</v>
-      </c>
-      <c r="G11" t="n">
-        <v>234</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.44</v>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1901</v>
+        <v>26100</v>
       </c>
       <c r="K11" t="n">
-        <v>2050</v>
+        <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>2080</v>
+        <v>30300</v>
       </c>
       <c r="M11" t="n">
-        <v>1907</v>
+        <v>25400</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>41189868896</v>
+        <v>321928620875</v>
       </c>
       <c r="P11" t="n">
-        <v>4795</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1524</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>-389000</v>
+        <v>20000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승 관련 전쟁 테마주로 부각되며 단기 급등 기대감 형성. VLCC 용선료 폭등 및 유가 200달러 전망 언급.</t>
+          <t>신규 상장 종목으로 전설이 될 것이라는 기대감. 외인 매수세 유입 관측. 단기 급등 후 하락 마감에 대한 아쉬움과 함께 종가 부근에서의 변동성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['전쟁 테마주', '유가 상승', 'VLCC']</t>
+          <t>['신규상장', '외인매수', '급등주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53400</v>
+        <v>90700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.44</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>147</v>
+        <v>853</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>23.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,139 +1515,139 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>53200</v>
+        <v>89900</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N12" t="n">
-        <v>3.36</v>
+        <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>93373000000</v>
+        <v>156396319350</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>128000</v>
+        <v>-289000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>70000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>미국 투자 협상 및 중동 에너지 공급망 이슈 관련 긍정적 뉴스 언급. 수주 잔고 증가 및 원전 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7990</v>
+        <v>1904</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>104</v>
+        <v>239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.52</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7990</v>
+        <v>1901</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="N13" t="n">
-        <v>0.46</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>82907000000</v>
+        <v>42100775181</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R13" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>594억 공급 계약 재료와 함께 포스코 지정 가공센터로서의 역할 언급. 품절주 특성 및 신고가 경신에 대한 기대감 형성. 텐배거 관련 언급.</t>
+          <t>홍해 사태 관련 전쟁 테마주로 급등 기대감. VLCC 용선료 폭등 및 유가 상승 수혜 전망. 다만, 개별 움직임에 대한 의문 제기도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공급 계약', '포스코', '품절주']</t>
+          <t>['전쟁테마주', '유가상승', 'VLCC']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H14" t="n">
         <v>38.02</v>
@@ -1714,7 +1714,7 @@
         <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>53641840000</v>
+        <v>54891104750</v>
       </c>
       <c r="P14" t="n">
         <v>822000</v>
@@ -1723,10 +1723,10 @@
         <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50400</v>
+        <v>3910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.09</v>
+        <v>-0.53</v>
       </c>
       <c r="E15" t="n">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>583</v>
+        <v>192</v>
       </c>
       <c r="H15" t="n">
-        <v>38.78</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>50800</v>
+        <v>3925</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3810</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3760</v>
       </c>
       <c r="N15" t="n">
-        <v>38.69</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>91502248839</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-163000</v>
+        <v>-582000</v>
       </c>
       <c r="S15" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '공시', '대규모']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29550</v>
+        <v>3600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H16" t="n">
-        <v>25.55</v>
+        <v>0.73</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29800</v>
+        <v>3620</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3520</v>
       </c>
       <c r="N16" t="n">
-        <v>24.99</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>46496472347</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R16" t="n">
-        <v>410000</v>
+        <v>-36000</v>
       </c>
       <c r="S16" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3890</v>
+        <v>50400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.53</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G17" t="n">
-        <v>188</v>
+        <v>585</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>38.78</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3925</v>
+        <v>50800</v>
       </c>
       <c r="K17" t="n">
-        <v>3810</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4180</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3760</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>38.69</v>
       </c>
       <c r="O17" t="n">
-        <v>90568837553</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-582000</v>
+        <v>-163000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6G 통신 관련주로 부각되며 개발 기대감 형성. 젠슨 황 발언 및 데이터센터 6G 연관성 언급. 장난질 심한 움직임에 대한 불만 제기.</t>
+          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['6G 통신', '데이터센터', '개발 기대']</t>
+          <t>['수주', '공시', '대규모']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8840</v>
+        <v>29550</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="H18" t="n">
-        <v>27.19</v>
+        <v>25.55</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8970</v>
+        <v>29800</v>
       </c>
       <c r="K18" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>8880</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>27.16</v>
+        <v>24.99</v>
       </c>
       <c r="O18" t="n">
-        <v>16537536025</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-34000</v>
+        <v>410000</v>
       </c>
       <c r="S18" t="n">
-        <v>-198000</v>
+        <v>-200000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>LG디스플레이에 대한 극도의 부정적 감정 표현. 20년 누적 손실 및 주가 회복 실패에 대한 비판. 3분기 영업이익 전망치 언급.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '영업이익', '주가 부진']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>192900</v>
+        <v>8850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="H19" t="n">
-        <v>75.98999999999999</v>
+        <v>27.19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>197500</v>
+        <v>8970</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8880</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N19" t="n">
-        <v>75.92</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>429194000000</v>
+        <v>16868960115</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-1070000</v>
+        <v>-34000</v>
       </c>
       <c r="S19" t="n">
-        <v>-84000</v>
+        <v>-198000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,99 +2212,99 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14120</v>
+        <v>51800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-0.44</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>601</v>
+        <v>147</v>
       </c>
       <c r="H20" t="n">
-        <v>5.98</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14600</v>
+        <v>53200</v>
       </c>
       <c r="K20" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6.09</v>
+        <v>3.36</v>
       </c>
       <c r="O20" t="n">
-        <v>99710395820</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-290000</v>
+        <v>128000</v>
       </c>
       <c r="S20" t="n">
-        <v>-96000</v>
+        <v>24000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원전 섹터 테마와 관련하여 자포리 원전 이슈 언급. 모건스탠리의 대규모 매도세로 인한 하락 우려.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전 섹터', '자포리 원전', '모건스탠리']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1792000</v>
+        <v>1803000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G21" t="n">
-        <v>1665</v>
+        <v>1729</v>
       </c>
       <c r="H21" t="n">
         <v>50.55</v>
@@ -2343,28 +2343,28 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1853000</v>
+        <v>1856000</v>
       </c>
       <c r="K21" t="n">
-        <v>1773000</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1795000</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1768000</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3130225130000</v>
+        <v>3267171000000</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>305500</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>-402000</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>CPI 발표 및 금리 변동성에 따른 주가 변동성 우려. 다음 주 추가 하락 가능성 언급.</t>
+          <t>개인 투자자 강매수세 및 기관 매수세 유입 확인. CPI 발표 및 금리 인상 가능성에도 불구하고 주가 상승 기대감 존재. 네이버 증권 시스템 변화에 대한 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['CPI', '금리', '박스권']</t>
+          <t>['기관매수', 'CPI', '금리인상']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,83 +2403,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7420</v>
+        <v>12220</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>449</v>
+        <v>105</v>
       </c>
       <c r="H22" t="n">
-        <v>11.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7680</v>
+        <v>12630</v>
       </c>
       <c r="K22" t="n">
-        <v>7540</v>
+        <v>12520</v>
       </c>
       <c r="L22" t="n">
-        <v>7660</v>
+        <v>12930</v>
       </c>
       <c r="M22" t="n">
-        <v>7360</v>
+        <v>12010</v>
       </c>
       <c r="N22" t="n">
-        <v>11.62</v>
+        <v>0.14</v>
       </c>
       <c r="O22" t="n">
-        <v>9832498825</v>
+        <v>62657485595</v>
       </c>
       <c r="P22" t="n">
-        <v>8850</v>
+        <v>20850</v>
       </c>
       <c r="Q22" t="n">
-        <v>4220</v>
+        <v>4020</v>
       </c>
       <c r="R22" t="n">
-        <v>51000</v>
+        <v>-106000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
+          <t>삼미금속, 테마주로서의 움직임 둔화 및 하락 추세, 원전 테마로의 수급 쏠림 현상.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '신영증권', '주가상승']</t>
+          <t>['테마주', '하락추세', '원전']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14190</v>
+        <v>14120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>306</v>
+        <v>620</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>5.98</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14740</v>
+        <v>14600</v>
       </c>
       <c r="K23" t="n">
-        <v>14050</v>
+        <v>14800</v>
       </c>
       <c r="L23" t="n">
-        <v>14560</v>
+        <v>14950</v>
       </c>
       <c r="M23" t="n">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="N23" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="O23" t="n">
-        <v>57381365965</v>
+        <v>101001595260</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q23" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R23" t="n">
-        <v>-282000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-19000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
+          <t>우리기술, 원전 섹터 관련 논의 속 단기 과열 및 급락 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '대장주']</t>
+          <t>['원전', '단기과열', '매도']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15040</v>
+        <v>259500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>505</v>
       </c>
       <c r="G24" t="n">
-        <v>267</v>
+        <v>1785</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>15640</v>
+        <v>269500</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>46.81</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2491825000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2643,27 +2643,27 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>16000</v>
+        <v>-2974000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-1056000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>서남권 반도체 클러스터 조기 생산 전망 및 외국인 프로그램 매수세 유입. 건설 부지 추가 확보 검토.</t>
+          <t>국내 증권 정보 및 플랫폼에 대한 불만 고조. 정치적 이슈와 연계된 언급 다수. 반도체 업황에 대한 부정적 전망과 주가 부진에 대한 답답함 표출.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '건설', '외국인']</t>
+          <t>['반도체', '증권정보', '주가부진']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,90 +2672,90 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>258500</v>
+        <v>14190</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.90%</t>
+          <t>-3.73%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="F25" t="n">
-        <v>507</v>
+        <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>1796</v>
+        <v>308</v>
       </c>
       <c r="H25" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>269000</v>
+        <v>14740</v>
       </c>
       <c r="K25" t="n">
-        <v>258000</v>
+        <v>14050</v>
       </c>
       <c r="L25" t="n">
-        <v>261000</v>
+        <v>14560</v>
       </c>
       <c r="M25" t="n">
-        <v>256500</v>
+        <v>14030</v>
       </c>
       <c r="N25" t="n">
-        <v>46.81</v>
+        <v>2.89</v>
       </c>
       <c r="O25" t="n">
-        <v>2435714825000</v>
+        <v>58149745015</v>
       </c>
       <c r="P25" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q25" t="n">
-        <v>72100</v>
+        <v>1272</v>
       </c>
       <c r="R25" t="n">
-        <v>-2974000</v>
+        <v>-282000</v>
       </c>
       <c r="S25" t="n">
-        <v>-1056000</v>
+        <v>-19000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 이슈와 함께 주가 하락에 대한 불만 표출. 반도체 수출 최대치와 주가 하락 간의 괴리감 언급.</t>
+          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['정치 테마주', '반도체', '주가 하락']</t>
+          <t>['광통신', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,90 +2764,90 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12100</v>
+        <v>15040</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.20%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12630</v>
+        <v>15640</v>
       </c>
       <c r="K26" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>61919289430</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-106000</v>
+        <v>16000</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>가스터빈 관련주로 언급되나, 수급 쏠림 및 원전 테마주 대비 약세. 계단식 하락 및 거래량 부진으로 인한 약세 전망. 넥스트장 기대감 언급.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전 테마', '거래량 부진']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,90 +2856,90 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7810</v>
+        <v>193900</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-5.90%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="F27" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="G27" t="n">
-        <v>975</v>
+        <v>149</v>
       </c>
       <c r="H27" t="n">
-        <v>1.29</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>8300</v>
+        <v>203000</v>
       </c>
       <c r="K27" t="n">
-        <v>8400</v>
+        <v>195000</v>
       </c>
       <c r="L27" t="n">
-        <v>8700</v>
+        <v>195600</v>
       </c>
       <c r="M27" t="n">
-        <v>7540</v>
+        <v>191000</v>
       </c>
       <c r="N27" t="n">
-        <v>1.17</v>
+        <v>75.92</v>
       </c>
       <c r="O27" t="n">
-        <v>27476786640</v>
+        <v>441225585300</v>
       </c>
       <c r="P27" t="n">
-        <v>21500</v>
+        <v>243500</v>
       </c>
       <c r="Q27" t="n">
-        <v>2300</v>
+        <v>58600</v>
       </c>
       <c r="R27" t="n">
-        <v>-73000</v>
+        <v>-1070000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-84000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>9월 14일 세계폐암학회(WCLC) 센딥파텔 교수 발표 데이터 기반 주가 대폭등 기대. 외국계 증권사 매수 유입.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['임상시험', '데이터', '학회']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,38 +2948,38 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3585</v>
+        <v>7860</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-5.30%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E28" t="n">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="G28" t="n">
-        <v>134</v>
+        <v>1030</v>
       </c>
       <c r="H28" t="n">
-        <v>0.73</v>
+        <v>1.29</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2987,235 +2987,235 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3865</v>
+        <v>8300</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>7540</v>
       </c>
       <c r="N28" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="O28" t="n">
-        <v>46066000000</v>
+        <v>28136683005</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="R28" t="n">
-        <v>-36000</v>
+        <v>-73000</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>페니트리움바이오, 9월 14일 WCLC 학회 발표 기반 대폭등 기대감, 임상 데이터 발표 주목.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['WCLC', '임상데이터', '폐암']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>233500</v>
+        <v>9280</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-7.71%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="F29" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="G29" t="n">
-        <v>849</v>
+        <v>324</v>
       </c>
       <c r="H29" t="n">
-        <v>7.58</v>
+        <v>4.49</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>253000</v>
+        <v>9800</v>
       </c>
       <c r="K29" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8.539999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="O29" t="n">
-        <v>191585250250</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-415000</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 관련 공매도 세력의 압박 속 주가 하락. 기관 매수세 유입.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['TC본더', '수출', '공매도']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26350</v>
+        <v>234000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-13.04%</t>
+          <t>-7.51%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E30" t="n">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="F30" t="n">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="G30" t="n">
-        <v>470</v>
+        <v>863</v>
       </c>
       <c r="H30" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>30300</v>
+        <v>253000</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N30" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>320183000000</v>
+        <v>195334801000</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R30" t="n">
-        <v>20000</v>
+        <v>-415000</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>종목에 대한 긍정적, 부정적 의견 혼재. 외인 유입 언급 있으나 하락 마감. 명확한 근거 부족.</t>
+          <t>9월 TC본더 수출 데이터 관련 공매도 세력의 압박 속 주가 하락. 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['외인 유입', '종목 토론']</t>
+          <t>['TC본더', '수출', '공매도']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_13.xlsx
+++ b/data/trending_integrated_20260911_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12610</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>207966000000</v>
+        <v>208024974845</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
         <v>-71000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 지목에 따른 관련주 부각. 594억 공급 계약 및 모건스텐리 매집 공시 확인. 양자+보안 유일 대장주로서 강한 상승 기대.</t>
+          <t>AI 다음 핵심 시장으로 사이버 보안 부문 지목. 젠슨 황 발언에 따른 보안 섹터 급등 및 엑스게이트 수혜 전망. 594억 공급계약 및 모건스텐리 매집 호재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '공급 계약']</t>
+          <t>['사이버 보안', '젠슨 황', '공급계약']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16310</v>
+        <v>2720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.26%</t>
+          <t>+29.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.19</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>13340</v>
+        <v>2095</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="N3" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="O3" t="n">
-        <v>131885000000</v>
+        <v>8068548084</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>8150</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>기관 연속 매집 확인에 따른 주가 상승 기대감. 전고점 돌파 및 2만원 이상 상승 전망. 다만, 추격 매수에 대한 경계와 주가 변동성에 대한 언급도 있음.</t>
+          <t>신약 기술이전 관련 1천억 선급금 유입 기대. 글로벌 제약사 7~8곳 접촉 사실 확인.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['기관매집', '상승전망', '전고점돌파']</t>
+          <t>['신약 기술 이전', '빅파마', '3자배정 유증']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>065170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2580</v>
+        <v>16670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.41%</t>
+          <t>+24.96%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>101345230109</v>
+        <v>139776000000</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-2091000</v>
+        <v>36000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
+          <t>K-뷰티 대장주로서의 기대감과 함께 급등세 지속 전망. 경영권 이슈 및 전고점 돌파 기대감 반영. 알바 언급 및 매수세 유입 추측.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
+          <t>['K-뷰티', '대장주', '경영권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,46 +832,46 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>003350</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>139000</v>
+        <v>2565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.52%</t>
+          <t>+20.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>282</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>116300</v>
+        <v>2135</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>467374000000</v>
+        <v>102341000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>제품 공급 부족 및 3상 가능성에 대한 기대감. 애플 관련 호재 가능성 언급. 단기 급등 후 거래량 부진.</t>
+          <t>594억 공급 계약 및 모건스탠리 48만주 매집 공시 확인. 미국 정부 양자컴퓨터 보조금 지원 관련 기대감. 거래량 증가와 함께 손바뀜 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공급 부족', '3상', '애플']</t>
+          <t>['공급계약', '양자컴퓨터', '매집공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7350</v>
+        <v>137800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.87%</t>
+          <t>+19.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="G6" t="n">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6570</v>
+        <v>115700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>4.58</v>
       </c>
       <c r="O6" t="n">
-        <v>160120000000</v>
+        <v>474732886400</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R6" t="n">
-        <v>110000</v>
+        <v>39000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>KoAct 광통신&amp;위성네트워크액티브 편입 및 대장주로서의 부각. 공매도 세력의 튀는 움직임 확인. 주가 상승에 대한 기대감과 함께 매수 타이밍에 대한 고민 존재.</t>
+          <t>부품 품귀 현상에 따른 실적 개선 기대감 형성. 거래량 부진 속 상한가 기대감 및 주가 급등 가능성 언급. 애플 관련주 편입 가능성 시사.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '위성네트워크', '대장주']</t>
+          <t>['품귀 현상', '실적 개선', '애플']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>7330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+9.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.79</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>452</v>
+        <v>362</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>2.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>161759739755</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R7" t="n">
-        <v>51000</v>
+        <v>110000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
+          <t>광통신 및 위성네트워크 섹터의 대장주로 부각되며 상승 기대감 형성. 보안 관련 이슈 및 공매도 세력 약화 분석. 급등 가능성 및 월요일 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '신영증권', '주가상승']</t>
+          <t>['광통신', '위성네트워크', '보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14980</v>
+        <v>15070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3.24%</t>
+          <t>+3.86%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F8" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="G8" t="n">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="H8" t="n">
         <v>3.14</v>
@@ -1156,13 +1156,13 @@
         <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>14910</v>
+        <v>14840</v>
       </c>
       <c r="N8" t="n">
         <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>199279109575</v>
+        <v>202301747045</v>
       </c>
       <c r="P8" t="n">
         <v>36200</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금강철강</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7920</v>
+        <v>3935</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+2.99%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="H9" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7690</v>
+        <v>3810</v>
       </c>
       <c r="K9" t="n">
-        <v>7670</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9170</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7450</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.46</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>84453932175</v>
+        <v>92162000000</v>
       </c>
       <c r="P9" t="n">
-        <v>9170</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-2000</v>
+        <v>-582000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>금강철강, 594억 공급계약 관련 급등 기대감 및 신고가 경신. 품절주 특성으로 인한 변동성 우려.</t>
+          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['품절주', '공급계약', '신고가']</t>
+          <t>['6G통신', '광통신', '데이터센터']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>053260</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19870</v>
+        <v>26500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="G10" t="n">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>0.32</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>26100</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>104981000000</v>
+        <v>322745760500</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-76000</v>
+        <v>20000</v>
       </c>
       <c r="S10" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 운동 독려 및 공매도 세력과의 전쟁 선포. 원전 8기 대미 투자 관련 뉴스 언급. 목표가 상향 소식과 함께 2만원 이상 주가 상승 기대.</t>
+          <t>신규 상장 종목으로 전설이 될 것이라는 기대감. 외인 매수세 유입 관측. 단기 급등 후 하락 마감에 대한 아쉬움과 함께 종가 부근에서의 변동성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '원전']</t>
+          <t>['신규상장', '외인매수', '급등주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26500</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="F11" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
-        <v>472</v>
+        <v>865</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32</v>
+        <v>7.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26100</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>321928620875</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>20000</v>
+        <v>-415000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-42000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신규 상장 종목으로 전설이 될 것이라는 기대감. 외인 매수세 유입 관측. 단기 급등 후 하락 마감에 대한 아쉬움과 함께 종가 부근에서의 변동성 언급.</t>
+          <t>9월 TC본더 수출 데이터 관련 공매도 세력의 압박 속 주가 하락. 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신규상장', '외인매수', '급등주']</t>
+          <t>['TC본더', '수출', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90700</v>
+        <v>90500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>853</v>
+        <v>875</v>
       </c>
       <c r="H12" t="n">
         <v>23.59</v>
@@ -1530,7 +1530,7 @@
         <v>23.65</v>
       </c>
       <c r="O12" t="n">
-        <v>156396319350</v>
+        <v>158942231100</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1904</v>
+        <v>19800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>239</v>
+        <v>509</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>10.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1901</v>
+        <v>19750</v>
       </c>
       <c r="K13" t="n">
-        <v>2050</v>
+        <v>19500</v>
       </c>
       <c r="L13" t="n">
-        <v>2080</v>
+        <v>19960</v>
       </c>
       <c r="M13" t="n">
-        <v>1900</v>
+        <v>19060</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>42100775181</v>
+        <v>107993541580</v>
       </c>
       <c r="P13" t="n">
-        <v>4795</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1524</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>홍해 사태 관련 전쟁 테마주로 급등 기대감. VLCC 용선료 폭등 및 유가 상승 수혜 전망. 다만, 개별 움직임에 대한 의문 제기도 존재.</t>
+          <t>대차 해지 운동 독려 및 공매도 세력과의 전쟁 선포. 원전 8기 대미 투자 관련 뉴스 언급. 목표가 상향 소식과 함께 2만원 이상 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['전쟁테마주', '유가상승', 'VLCC']</t>
+          <t>['대차해지', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>415500</v>
+        <v>1905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="H14" t="n">
-        <v>38.02</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,28 +1699,28 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>415500</v>
+        <v>1901</v>
       </c>
       <c r="K14" t="n">
-        <v>407000</v>
+        <v>2050</v>
       </c>
       <c r="L14" t="n">
-        <v>418000</v>
+        <v>2080</v>
       </c>
       <c r="M14" t="n">
-        <v>404000</v>
+        <v>1900</v>
       </c>
       <c r="N14" t="n">
-        <v>37.82</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>54891104750</v>
+        <v>42359562934</v>
       </c>
       <c r="P14" t="n">
-        <v>822000</v>
+        <v>4795</v>
       </c>
       <c r="Q14" t="n">
-        <v>283000</v>
+        <v>1524</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1730,20 +1730,20 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
+          <t>홍해 사태 관련 전쟁 테마주로 부각되며 급등 기대감 형성. VLCC 용선료 폭등 및 유가 상승 수혜 전망. 프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주', '로봇', '미래차']</t>
+          <t>['홍해 사태', '전쟁 테마주', 'VLCC']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3910</v>
+        <v>415500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.53</v>
+        <v>0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>192</v>
+        <v>273</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>38.02</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3925</v>
+        <v>415500</v>
       </c>
       <c r="K15" t="n">
-        <v>3810</v>
+        <v>407000</v>
       </c>
       <c r="L15" t="n">
-        <v>4180</v>
+        <v>418000</v>
       </c>
       <c r="M15" t="n">
-        <v>3760</v>
+        <v>404000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>37.82</v>
       </c>
       <c r="O15" t="n">
-        <v>91502248839</v>
+        <v>56023608250</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>822000</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>283000</v>
       </c>
       <c r="R15" t="n">
-        <v>-582000</v>
+        <v>23000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6G 통신 및 광통신 대세 수혜 기대감. 젠슨 황 발언과 연계된 데이터센터 수요 증가 전망. 단기 급등 가능성에 대한 기대와 함께 장난질에 대한 경계 필요.</t>
+          <t>아틀라스 관절부품 전량 수주 및 그룹사 양산 로드맵 가동. 미래 기술 60종 공개로 로봇 분야 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['6G통신', '광통신', '데이터센터']</t>
+          <t>['수주', '로봇', '미래차']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3600</v>
+        <v>50400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>139</v>
+        <v>597</v>
       </c>
       <c r="H16" t="n">
-        <v>0.73</v>
+        <v>38.78</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3620</v>
+        <v>50800</v>
       </c>
       <c r="K16" t="n">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3915</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3520</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.54</v>
+        <v>38.69</v>
       </c>
       <c r="O16" t="n">
-        <v>46496472347</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4335</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-36000</v>
+        <v>-163000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['수주', '공시', '대규모']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50400</v>
+        <v>29550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="F17" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>585</v>
+        <v>147</v>
       </c>
       <c r="H17" t="n">
-        <v>38.78</v>
+        <v>25.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>50800</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>38.69</v>
+        <v>24.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1999,67 +1999,67 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-163000</v>
+        <v>410000</v>
       </c>
       <c r="S17" t="n">
-        <v>31000</v>
+        <v>-200000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모 대규모 수주 공시 확인. 사우디·베트남 겹호재 및 외국인 매수세 유입 기대.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '공시', '대규모']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29550</v>
+        <v>8870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="H18" t="n">
-        <v>25.55</v>
+        <v>27.19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,143 +2067,143 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29800</v>
+        <v>8970</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>8780</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8880</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>8680</v>
       </c>
       <c r="N18" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>17308543850</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>410000</v>
+        <v>-34000</v>
       </c>
       <c r="S18" t="n">
-        <v>-200000</v>
+        <v>-198000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['경영부진', '주가하락', '디스플레이']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8850</v>
+        <v>14120</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
-        <v>274</v>
+        <v>632</v>
       </c>
       <c r="H19" t="n">
-        <v>27.19</v>
+        <v>5.98</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8970</v>
+        <v>14320</v>
       </c>
       <c r="K19" t="n">
-        <v>8780</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8880</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>8680</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>6.09</v>
       </c>
       <c r="O19" t="n">
-        <v>16868960115</v>
+        <v>102433000000</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-34000</v>
+        <v>-290000</v>
       </c>
       <c r="S19" t="n">
-        <v>-198000</v>
+        <v>-96000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 경영 부진 및 주가 하락에 대한 강한 불만 표출. 20년간 28조 손실 언급. 디스플레이 패널 업황 악화 및 금리 인상 가능성으로 인한 하락 전망.</t>
+          <t>자포리 원전 이슈 및 미국 원전 섹터 강세에 따른 기대감 형성. 모건스텐리 대규모 매수세 유입 및 120일선 지지선 중요성 강조. 원전 섹터 주도주 역할 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영부진', '주가하락', '디스플레이']</t>
+          <t>['원전', '자포리', '모건스텐리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,46 +2212,46 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>금강철강</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51800</v>
+        <v>7860</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.44</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>0.52</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>53200</v>
+        <v>7990</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.36</v>
+        <v>0.46</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>85368000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,36 +2275,36 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>128000</v>
+        <v>-2000</v>
       </c>
       <c r="S20" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>포스코 지정 가공센터로서 공급 계약 체결 및 실적 기대감 형성. 유통물량 부족에 따른 급등 가능성 언급. 단기 급락 및 변동성 경계 신호.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['공급 계약', '포스코', '품절주']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>053260</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1803000</v>
+        <v>1808000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G21" t="n">
-        <v>1729</v>
+        <v>1813</v>
       </c>
       <c r="H21" t="n">
         <v>50.55</v>
@@ -2343,28 +2343,28 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1812000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N21" t="n">
         <v>50.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3267171000000</v>
+        <v>3392515257000</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R21" t="n">
         <v>-402000</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>개인 투자자 강매수세 및 기관 매수세 유입 확인. CPI 발표 및 금리 인상 가능성에도 불구하고 주가 상승 기대감 존재. 네이버 증권 시스템 변화에 대한 언급.</t>
+          <t>미국 증시 대비 선방 및 기관 매수세 유입 긍정적. CPI 발표 및 중동 평화 회담 등 거시 경제 변수 주목. 다음주 상승 및 박스권 돌파 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['기관매수', 'CPI', '금리인상']</t>
+          <t>['CPI', '기관 매수', '박스권']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,123 +2403,123 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12220</v>
+        <v>51800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>-2.63%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>-0.44</v>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>12630</v>
+        <v>53200</v>
       </c>
       <c r="K22" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.14</v>
+        <v>3.36</v>
       </c>
       <c r="O22" t="n">
-        <v>62657485595</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-106000</v>
+        <v>128000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼미금속, 테마주로서의 움직임 둔화 및 하락 추세, 원전 테마로의 수급 쏠림 현상.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['테마주', '하락추세', '원전']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14120</v>
+        <v>12210</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.29%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.11</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
+        <v>98</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
         <v>107</v>
       </c>
-      <c r="F23" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" t="n">
-        <v>620</v>
-      </c>
       <c r="H23" t="n">
-        <v>5.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14600</v>
+        <v>12630</v>
       </c>
       <c r="K23" t="n">
-        <v>14800</v>
+        <v>12520</v>
       </c>
       <c r="L23" t="n">
-        <v>14950</v>
+        <v>12930</v>
       </c>
       <c r="M23" t="n">
-        <v>14020</v>
+        <v>12010</v>
       </c>
       <c r="N23" t="n">
-        <v>6.09</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>101001595260</v>
+        <v>62919477650</v>
       </c>
       <c r="P23" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q23" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>우리기술, 원전 섹터 관련 논의 속 단기 과열 및 급락 우려.</t>
+          <t>원전 테마주 중 한전기술 등과 비교되며 상대적 약세. 넥스트장 기대감에도 불구하고 거래량 부진 및 주가 하락세 지속. 가스터빈 공급과잉 우려 및 추세 전환 어려움 전망.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['원전', '단기과열', '매도']</t>
+          <t>['원전', '가스터빈', '거래량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>259500</v>
+        <v>14230</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.71%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="F24" t="n">
-        <v>505</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>1785</v>
+        <v>312</v>
       </c>
       <c r="H24" t="n">
-        <v>46.71</v>
+        <v>2.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>269500</v>
+        <v>14740</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N24" t="n">
-        <v>46.81</v>
+        <v>2.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2491825000000</v>
+        <v>58995229930</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R24" t="n">
-        <v>-2974000</v>
+        <v>-282000</v>
       </c>
       <c r="S24" t="n">
-        <v>-1056000</v>
+        <v>-19000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>국내 증권 정보 및 플랫폼에 대한 불만 고조. 정치적 이슈와 연계된 언급 다수. 반도체 업황에 대한 부정적 전망과 주가 부진에 대한 답답함 표출.</t>
+          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체', '증권정보', '주가부진']</t>
+          <t>['광통신', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,77 +2672,77 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14190</v>
+        <v>7410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F25" t="n">
         <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>308</v>
+        <v>455</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>11.72</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>14740</v>
+        <v>7680</v>
       </c>
       <c r="K25" t="n">
-        <v>14050</v>
+        <v>7540</v>
       </c>
       <c r="L25" t="n">
-        <v>14560</v>
+        <v>7660</v>
       </c>
       <c r="M25" t="n">
-        <v>14030</v>
+        <v>7360</v>
       </c>
       <c r="N25" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="O25" t="n">
-        <v>58149745015</v>
+        <v>10300343865</v>
       </c>
       <c r="P25" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q25" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R25" t="n">
-        <v>-282000</v>
+        <v>51000</v>
       </c>
       <c r="S25" t="n">
-        <v>-19000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>광통신 대장주로서의 지위 재확인 및 외국인 매수세 유입 언급. 오후 흐름 및 월요일 강한 상승 기대감 형성. 2만원 목표가 제시.</t>
+          <t>광주 반도체 관련 기사 및 신영증권 창구 매수세 유입 관측. 주가 상승 기대감 존재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '대장주']</t>
+          <t>['반도체', '신영증권', '주가상승']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15040</v>
+        <v>259500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>504</v>
       </c>
       <c r="G26" t="n">
-        <v>281</v>
+        <v>1793</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>15640</v>
+        <v>269000</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>256500</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>46.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2555971700500</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R26" t="n">
-        <v>16000</v>
+        <v>-2974000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-1056000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
+          <t>정치적 이슈와 연관된 언급 다수. 반도체 섹터 전반의 부진 및 상대적 약세에 대한 불만 표출. 네이버 증권 게시판 시스템에 대한 비판.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
+          <t>['반도체', '정치 테마', '증권 시스템']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>193900</v>
+        <v>15040</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F27" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="H27" t="n">
-        <v>75.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,51 +2895,51 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>203000</v>
+        <v>15640</v>
       </c>
       <c r="K27" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>75.92</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>441225585300</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-1070000</v>
+        <v>16000</v>
       </c>
       <c r="S27" t="n">
-        <v>-84000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
+          <t>금호건설, 서남권 반도체 클러스터 및 폐기물 처리 사업 관련 논의, 외국인 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
+          <t>['반도체클러스터', '폐기물처리', '외국인']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,90 +2948,90 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7860</v>
+        <v>194000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-5.30%</t>
+          <t>-4.43%</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="F28" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="G28" t="n">
-        <v>1030</v>
+        <v>150</v>
       </c>
       <c r="H28" t="n">
-        <v>1.29</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>8300</v>
+        <v>203000</v>
       </c>
       <c r="K28" t="n">
-        <v>8400</v>
+        <v>195000</v>
       </c>
       <c r="L28" t="n">
-        <v>8700</v>
+        <v>195600</v>
       </c>
       <c r="M28" t="n">
-        <v>7540</v>
+        <v>191000</v>
       </c>
       <c r="N28" t="n">
-        <v>1.17</v>
+        <v>75.92</v>
       </c>
       <c r="O28" t="n">
-        <v>28136683005</v>
+        <v>453686409300</v>
       </c>
       <c r="P28" t="n">
-        <v>21500</v>
+        <v>243500</v>
       </c>
       <c r="Q28" t="n">
-        <v>2300</v>
+        <v>58600</v>
       </c>
       <c r="R28" t="n">
-        <v>-73000</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 9월 14일 WCLC 학회 발표 기반 대폭등 기대감, 임상 데이터 발표 주목.</t>
+          <t>외국계 증권사 매도세 및 주가 하락에 대한 불만 표출. 특별 배당 기대감 속에서도 주가 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['WCLC', '임상데이터', '폐암']</t>
+          <t>['외국계 매도', '주가 하락', '특별 배당']</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -3062,13 +3062,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H29" t="n">
         <v>4.49</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -3139,83 +3139,83 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>234000</v>
+        <v>7760</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-7.51%</t>
+          <t>-6.51%</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.96</v>
+        <v>0.12</v>
       </c>
       <c r="E30" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F30" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G30" t="n">
-        <v>863</v>
+        <v>1085</v>
       </c>
       <c r="H30" t="n">
-        <v>7.58</v>
+        <v>1.29</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>253000</v>
+        <v>8300</v>
       </c>
       <c r="K30" t="n">
-        <v>241000</v>
+        <v>8400</v>
       </c>
       <c r="L30" t="n">
-        <v>241000</v>
+        <v>8700</v>
       </c>
       <c r="M30" t="n">
-        <v>231000</v>
+        <v>7540</v>
       </c>
       <c r="N30" t="n">
-        <v>8.539999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="O30" t="n">
-        <v>195334801000</v>
+        <v>28611732225</v>
       </c>
       <c r="P30" t="n">
-        <v>426000</v>
+        <v>21500</v>
       </c>
       <c r="Q30" t="n">
-        <v>86100</v>
+        <v>2300</v>
       </c>
       <c r="R30" t="n">
-        <v>-415000</v>
+        <v>-73000</v>
       </c>
       <c r="S30" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9월 TC본더 수출 데이터 관련 공매도 세력의 압박 속 주가 하락. 기관 매수세 유입.</t>
+          <t>WCLC 학회 센딥파텔 교수 발표에 따른 주가 대폭등 기대. 외국계 증권사 유입 확인.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>['TC본더', '수출', '공매도']</t>
+          <t>['WCLC', '임상 시험', '기술 수출']</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3224,7 +3224,99 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>187660</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3565</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-7.76%</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>64</v>
+      </c>
+      <c r="F31" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" t="n">
+        <v>144</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3865</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O31" t="n">
+        <v>46814000000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>['폭락', '주주', '전망']</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>067290</t>
         </is>
       </c>
     </row>
